--- a/stories/arbres/ATOM-VIV.ANI.001-09.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Thérèse arrive à la ferme avec papa. Une vache mange près de la barrière. Elle fait meuh. Papa dit : c'est une vache. C'est le nom de l'animal. Le cri, c'est meuh. Thérèse répète : une vache. Meuh. Un coq marche dans la cour. Il fait cocorico. Papa dit : c'est un coq. Le cri, c'est cocorico. Thérèse dit : un coq. Cocorico. Plus loin, un mouton frotte sa laine. Il fait bêê. Papa dit : c'est un mouton. Le cri, c'est bêê. Thérèse rit. Elle dit le nom de l'animal. Elle dit le cri. Vache, coq, mouton. Parce qu'elle a écouté, elle peut nommer.</t>
+          <t>Thérèse arrive à la ferme avec papa. Une vache mange près de la barrière. Elle fait meuh. C'est une vache. C'est le nom de l'animal. Le cri, c'est meuh. Thérèse répète : une vache. Meuh. Un coq marche dans la cour. Il fait cocorico. C'est un coq. Le cri, c'est cocorico. Un coq. Cocorico. Plus loin, un mouton frotte sa laine. Il fait bêê. C'est un mouton. Le cri, c'est bêê. Thérèse rit. Elle dit le nom de l'animal. Elle dit le cri. Vache, coq, mouton. Parce qu'elle a écouté, elle peut nommer.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,18 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Thérèse arrive à la ferme avec papa. Une vache mange près de la barrière. Elle fait meuh.
+papa|C'est une vache. C'est le nom de l'animal.
+narrateur|Le cri, c'est meuh. Thérèse répète : une vache. Meuh. Un coq marche dans la cour. Il fait cocorico.
+papa|C'est un coq.
+narrateur|Le cri, c'est cocorico.
+enfant-f|Un coq. Cocorico. Plus loin, un mouton frotte sa laine. Il fait bêê.
+papa|C'est un mouton.
+narrateur|Le cri, c'est bêê. Thérèse rit. Elle dit le nom de l'animal. Elle dit le cri. Vache, coq, mouton. Parce qu'elle a écouté, elle peut nommer.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1493,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Thérèse entend un animal. Que dit-elle ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1666,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Thérèse a dit le nom de l'animal. Elle a dit le cri. Vache. Coq. Mouton.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1833,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Thérèse donne la main à papa. La ferme sent le foin.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2000,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2040,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.001-09.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-09.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1317,6 +1322,11 @@
 narrateur|Le cri, c'est bêê. Thérèse rit. Elle dit le nom de l'animal. Elle dit le cri. Vache, coq, mouton. Parce qu'elle a écouté, elle peut nommer.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>enfants_parc</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1500,6 +1510,7 @@
           <t>narrateur|Thérèse entend un animal. Que dit-elle ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1671,6 +1682,7 @@
           <t>narrateur|Thérèse a dit le nom de l'animal. Elle a dit le cri. Vache. Coq. Mouton.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1838,6 +1850,7 @@
           <t>narrateur|Thérèse donne la main à papa. La ferme sent le foin.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2005,6 +2018,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2023,7 +2037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2047,6 +2061,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2089,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2248,6 +2276,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.ANI.001-09.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-09.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Thérèse nomme les cris à la ferme</t>
+          <t>Le veau derrière la barrière</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Victorino veut le veau. Il se cache. Un meuglement guide. Ils le trouvent du sentier, hors de l'enclos.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Thérèse arrive à la ferme avec papa. Une vache mange près de la barrière. Elle fait meuh. C'est une vache. C'est le nom de l'animal. Le cri, c'est meuh. Thérèse répète : une vache. Meuh. Un coq marche dans la cour. Il fait cocorico. C'est un coq. Le cri, c'est cocorico. Un coq. Cocorico. Plus loin, un mouton frotte sa laine. Il fait bêê. C'est un mouton. Le cri, c'est bêê. Thérèse rit. Elle dit le nom de l'animal. Elle dit le cri. Vache, coq, mouton. Parce qu'elle a écouté, elle peut nommer.</t>
+          <t>Le râtelier penche au bord du sentier. Un brin de foin tombe dans la poussière. Ça sent le lait tiède et la paille. Une corde usée pend au piquet. Tu sens le lait, Victorino ? Oui. Je veux le veau. Celui de l'enclos ? Je l'ai entendu. En ce moment, Victorino marche sur le sentier. Le bois de la barrière est chaud et rêche. L'enclos semble vide, tout calme. Il n'est pas là. On reste sur le chemin. On ne rentre pas dans l'enclos. Victorino pose les deux mains sur le bois. Un meuglement court arrive, tout bas. Là ! Tu as entendu ? Meuh, tout petit. Le veau meugle. Le cri vient du coin d'ombre. Un tas de paille cache un flanc roux. Il se cache. On le cherche du sentier ? Oui. Ils avancent le long de la barrière. Victorino ne passe pas la jambe. Le meuglement revient, plus clair. Meuh. C'est son cri. Une oreille bouge dans le foin. Puis un œil noir. Victorino se baisse pour mieux voir. Les genoux touchent la poussière du sentier. Il est petit. C'est un veau. Le foin cache encore le dos. Le sentier sent le lait, tout près. Il meugle encore. On avance le long du bois.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Thérèse arrive à la ferme avec papa. Une vache mange près de la barrière. Elle fait meuh. Papa dit : c'est une vache. C'est le &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt; de l'animal. Le cri, c'est meuh. Thérèse répète : une vache. Meuh. Un coq marche dans la cour. Il fait cocorico. Papa dit : c'est un coq. Le cri, c'est cocorico. Thérèse dit : un coq. Cocorico. Plus loin, un mouton frotte sa laine. Il fait bêê. Papa dit : c'est un mouton. Le cri, c'est bêê. Thérèse rit. Elle dit le nom de l'animal. Elle dit le cri. Vache, coq, mouton. Parce qu'elle a écouté, elle peut nommer.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le râtelier penche au bord du sentier. Un brin de foin tombe dans la poussière. Ça sent le lait tiède et la paille. Une corde usée pend au piquet. Tu sens le lait, Victorino ? Oui. Je veux le veau. Celui de l'enclos ? Je l'ai entendu. En ce moment, Victorino marche sur le sentier. Le bois de la barrière est chaud et rêche. L'enclos semble vide, tout calme. Il n'est pas là. On reste sur le chemin. On ne rentre pas dans l'enclos. Victorino pose les deux mains sur le bois. Un meuglement court arrive, tout bas. Là ! Tu as entendu ? Meuh, tout petit. Le veau meugle. Le cri vient du coin d'ombre. Un tas de paille cache un flanc roux. Il se cache. On le cherche du sentier ? Oui. Ils avancent le long de la barrière. Victorino ne passe pas la jambe. Le meuglement revient, plus clair. Meuh. C'est son cri. Une oreille bouge dans le foin. Puis un œil noir. Victorino se baisse pour mieux voir. Les genoux touchent la poussière du sentier. Il est petit. C'est un veau. Le foin cache encore le dos. Le sentier sent le lait, tout près. Il meugle encore. On avance le long du bois.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,14 +1324,47 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Thérèse arrive à la ferme avec papa. Une vache mange près de la barrière. Elle fait meuh.
-papa|C'est une vache. C'est le nom de l'animal.
-narrateur|Le cri, c'est meuh. Thérèse répète : une vache. Meuh. Un coq marche dans la cour. Il fait cocorico.
-papa|C'est un coq.
-narrateur|Le cri, c'est cocorico.
-enfant-f|Un coq. Cocorico. Plus loin, un mouton frotte sa laine. Il fait bêê.
-papa|C'est un mouton.
-narrateur|Le cri, c'est bêê. Thérèse rit. Elle dit le nom de l'animal. Elle dit le cri. Vache, coq, mouton. Parce qu'elle a écouté, elle peut nommer.</t>
+          <t>narrateur|Le râtelier penche au bord du sentier.
+narrateur|Un brin de foin tombe dans la poussière.
+narrateur|Ça sent le lait tiède et la paille.
+narrateur|Une corde usée pend au piquet.
+papa|Tu sens le lait, Victorino ?
+enfant-m|Oui.
+enfant-m|Je veux le veau.
+papa|Celui de l'enclos ?
+enfant-m|Je l'ai entendu.
+narrateur|En ce moment, Victorino marche sur le sentier.
+narrateur|Le bois de la barrière est chaud et rêche.
+narrateur|L'enclos semble vide, tout calme.
+enfant-m|Il n'est pas là.
+papa|On reste sur le chemin.
+papa|On ne rentre pas dans l'enclos.
+narrateur|Victorino pose les deux mains sur le bois.
+narrateur|Un meuglement court arrive, tout bas.
+enfant-m|Là !
+papa|Tu as entendu ?
+enfant-m|Meuh, tout petit.
+papa|Le veau meugle.
+narrateur|Le cri vient du coin d'ombre.
+narrateur|Un tas de paille cache un flanc roux.
+enfant-m|Il se cache.
+papa|On le cherche du sentier ?
+enfant-m|Oui.
+narrateur|Ils avancent le long de la barrière.
+narrateur|Victorino ne passe pas la jambe.
+narrateur|Le meuglement revient, plus clair.
+enfant-m|Meuh.
+papa|C'est son cri.
+narrateur|Une oreille bouge dans le foin.
+narrateur|Puis un œil noir.
+narrateur|Victorino se baisse pour mieux voir.
+narrateur|Les genoux touchent la poussière du sentier.
+enfant-m|Il est petit.
+papa|C'est un veau.
+narrateur|Le foin cache encore le dos.
+narrateur|Le sentier sent le lait, tout près.
+enfant-m|Il meugle encore.
+papa|On avance le long du bois.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
@@ -1351,27 +1396,27 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>Victorino entend meuh. Quel est le cri du veau ?</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Victorino entend meuh. Quel est le cri du veau ?</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>Thérèse entend un animal. Que dit-elle ?</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Thérèse entend un animal. Que dit-elle ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Thérèse entend un animal. Que dit-elle ?</t>
-        </is>
-      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>vache</t>
+          <t>meuh</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>vache | meuh | coq | cocorico | mouton | bêê</t>
+          <t>meuh | il meugle | meugle | le cri | le veau</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1386,7 +1431,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle dit le nom de l'animal. Elle dit le cri. Que dit Thérèse ?</t>
+          <t>Le veau meugle. Quel est le cri ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1428,14 +1473,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1507,10 +1552,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Thérèse entend un animal. Que dit-elle ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Victorino entend meuh.
+narrateur|Quel est le cri du veau ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1535,12 +1580,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Thérèse a dit le nom de l'animal. Elle a dit le cri. Vache. Coq. Mouton.</t>
+          <t>Le veau sort le museau du tas de paille. Il meugle encore, tout près de la barrière. Je le vois. Merci d'être resté sur le sentier. On regarde de dehors. Il meugle. Oui. Meuh. Victorino garde les mains sur le bois. Il ne glisse pas les doigts entre les planches. On reste hors de l'enclos ? Oui. Le veau mâche un brin, de l'autre côté. Sa langue est rose et rêche. Le râtelier penche encore un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Thérèse a dit le &lt;emphasis level="moderate"&gt;nom&lt;/emphasis&gt; de l'animal. Elle a dit le cri. Vache. Coq. Mouton.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le veau sort le museau du tas de paille. Il meugle encore, tout près de la barrière. Je le vois. Merci d'être resté sur le sentier. On regarde de dehors. Il meugle. Oui. Meuh. Victorino garde les mains sur le bois. Il ne glisse pas les doigts entre les planches. On reste hors de l'enclos ? Oui. Le veau mâche un brin, de l'autre côté. Sa langue est rose et rêche. Le râtelier penche encore un peu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1603,7 +1648,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1679,10 +1724,23 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Thérèse a dit le nom de l'animal. Elle a dit le cri. Vache. Coq. Mouton.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Le veau sort le museau du tas de paille.
+narrateur|Il meugle encore, tout près de la barrière.
+enfant-m|Je le vois.
+papa|Merci d'être resté sur le sentier.
+papa|On regarde de dehors.
+enfant-m|Il meugle.
+papa|Oui.
+papa|Meuh.
+narrateur|Victorino garde les mains sur le bois.
+narrateur|Il ne glisse pas les doigts entre les planches.
+papa|On reste hors de l'enclos ?
+enfant-m|Oui.
+narrateur|Le veau mâche un brin, de l'autre côté.
+narrateur|Sa langue est rose et rêche.
+narrateur|Le râtelier penche encore un peu.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1707,12 +1765,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Thérèse donne la main à papa. La ferme sent le foin.</t>
+          <t>Le flanc roux se lève tout entier. Le veau n'est plus caché. Il était sous la paille. Tu l'as trouvé avec les oreilles. Puis avec les yeux. Une corde usée tape le piquet. Victorino reste sur la poussière du chemin. Meuh. C'est son cri. Le lait tiède sent encore autour de l'enclos. Tu voulais le veau. Le voilà, de ce côté-ci. Un brin de foin tombe encore. Il s'accroche à la barre du râtelier. Il mâche. On le laisse. La poussière du sentier colle aux genoux.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Thérèse donne la &lt;emphasis level="moderate"&gt;main&lt;/emphasis&gt; à papa. La ferme sent le foin.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le flanc roux se lève tout entier. Le veau n'est plus caché. Il était sous la paille. Tu l'as trouvé avec les oreilles. Puis avec les yeux. Une corde usée tape le piquet. Victorino reste sur la poussière du chemin. Meuh. C'est son cri. Le lait tiède sent encore autour de l'enclos. Tu voulais le veau. Le voilà, de ce côté-ci. Un brin de foin tombe encore. Il s'accroche à la barre du râtelier. Il mâche. On le laisse. La poussière du sentier colle aux genoux.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1775,7 +1833,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1847,10 +1905,25 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Thérèse donne la main à papa. La ferme sent le foin.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le flanc roux se lève tout entier.
+narrateur|Le veau n'est plus caché.
+enfant-m|Il était sous la paille.
+papa|Tu l'as trouvé avec les oreilles.
+papa|Puis avec les yeux.
+narrateur|Une corde usée tape le piquet.
+narrateur|Victorino reste sur la poussière du chemin.
+enfant-m|Meuh.
+papa|C'est son cri.
+narrateur|Le lait tiède sent encore autour de l'enclos.
+papa|Tu voulais le veau.
+papa|Le voilà, de ce côté-ci.
+narrateur|Un brin de foin tombe encore.
+narrateur|Il s'accroche à la barre du râtelier.
+enfant-m|Il mâche.
+papa|On le laisse.
+narrateur|La poussière du sentier colle aux genoux.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1875,12 +1948,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Le veau mâche, de l'autre côté de la barrière. Victorino prend la main de papa. On l'a trouvé. Oui. Le sentier reste hors de l'enclos, tout clair.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le veau mâche, de l'autre côté de la barrière. Victorino prend la main de papa. On l'a trouvé. Oui. Le sentier reste hors de l'enclos, tout clair.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1943,7 +2016,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2015,10 +2088,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Le veau mâche, de l'autre côté de la barrière.
+narrateur|Victorino prend la main de papa.
+enfant-m|On l'a trouvé.
+papa|Oui.
+narrateur|Le sentier reste hors de l'enclos, tout clair.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2037,7 +2113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2075,6 +2151,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.001-09.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.001-09.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>ferme</t>
+          <t>ferme, sentier le long de l'enclos</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Thérèse, papa</t>
+          <t>Victorino, papa</t>
         </is>
       </c>
     </row>
